--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>70420.27</v>
+        <v>69563.86</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10987.16</v>
+        <v>10849.94</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>70017.3</v>
+        <v>70039.59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>566513-1-CM26</t>
+          <t>566513-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>69563.86</v>
+        <v>54888.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>886182-9-SE26</t>
+          <t>566513-1-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,78 +623,139 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10849.94</v>
+        <v>69563.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>886182-9-SE26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Universidad de Aysen</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>10849.94</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>886182-13-CM26</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2239-12-LR23</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>ene-2026</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>61.980.520-8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Universidad de Aysen</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Aysén</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>70039.59</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>566513-1-CM26</t>
+          <t>886182-4-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>69563.86</v>
+        <v>41777.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>886182-9-SE26</t>
+          <t>566513-1-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,78 +684,139 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10849.94</v>
+        <v>69563.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>886182-9-SE26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Universidad de Aysen</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>10849.94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>886182-13-CM26</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2239-12-LR23</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>ene-2026</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>61.980.520-8</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Universidad de Aysen</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Aysén</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>70039.59</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>566513-1-CM25</t>
+          <t>886182-4-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>54888.26</v>
+        <v>41777.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>886182-4-CM25</t>
+          <t>566513-1-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>41777.34</v>
+        <v>69563.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>566513-1-CM26</t>
+          <t>886182-9-SE26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,20 +684,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>69563.86</v>
+        <v>10849.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>886182-9-SE26</t>
+          <t>886182-13-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,12 +716,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -727,7 +731,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -745,78 +749,13 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10849.94</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>886182-13-CM26</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>61.980.520-8</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Universidad de Aysen</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
         <v>70039.59</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>886182-4-CM25</t>
+          <t>566513-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>41777.34</v>
+        <v>54888.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>566513-1-CM26</t>
+          <t>886182-4-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>69563.86</v>
+        <v>41777.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>886182-9-SE26</t>
+          <t>566513-1-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -703,71 +703,136 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10849.94</v>
+        <v>69563.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>886182-9-SE26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>10849.94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>886182-13-CM26</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2239-12-LR23</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>ene-2026</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>61.980.520-8</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Aysén</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Tarapacá</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>70039.59</v>
       </c>
     </row>
